--- a/Pharmacologie special/data/Maladies.xlsx
+++ b/Pharmacologie special/data/Maladies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Pharmacologie special\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1529574E-F5F3-4432-9696-EF9A300A1D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C6EF5B-1545-4907-8D8D-8099CFAC3D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{550D4594-D7DD-4F67-887A-DCF2F0E62F5B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="209">
   <si>
     <t>Pathologie</t>
   </si>
@@ -663,6 +663,9 @@
   </si>
   <si>
     <t>2eme intention_2</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -2041,6 +2044,9 @@
       <c r="D51" t="s">
         <v>189</v>
       </c>
+      <c r="E51" t="s">
+        <v>208</v>
+      </c>
       <c r="K51" t="s">
         <v>190</v>
       </c>

--- a/Pharmacologie special/data/Maladies.xlsx
+++ b/Pharmacologie special/data/Maladies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Pharmacologie special\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C6EF5B-1545-4907-8D8D-8099CFAC3D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6916F2C-EAC8-43CD-ACAD-B31A3712289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{550D4594-D7DD-4F67-887A-DCF2F0E62F5B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="208">
   <si>
     <t>Pathologie</t>
   </si>
@@ -663,9 +663,6 @@
   </si>
   <si>
     <t>2eme intention_2</t>
-  </si>
-  <si>
-    <t>a</t>
   </si>
 </sst>
 </file>
@@ -2044,9 +2041,6 @@
       <c r="D51" t="s">
         <v>189</v>
       </c>
-      <c r="E51" t="s">
-        <v>208</v>
-      </c>
       <c r="K51" t="s">
         <v>190</v>
       </c>

--- a/Pharmacologie special/data/Maladies.xlsx
+++ b/Pharmacologie special/data/Maladies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Pharmacologie special\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6916F2C-EAC8-43CD-ACAD-B31A3712289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FAF214-7AA9-4434-A35F-AFE1E31EE6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{550D4594-D7DD-4F67-887A-DCF2F0E62F5B}"/>
   </bookViews>
@@ -278,9 +278,6 @@
     <t>Antagoniste 5-HT &amp; Agoniste MT</t>
   </si>
   <si>
-    <t>Tricycliques (fait les 3 à la fois)</t>
-  </si>
-  <si>
     <t>Troubles bipolaires (Episodes maniaques)</t>
   </si>
   <si>
@@ -663,6 +660,9 @@
   </si>
   <si>
     <t>2eme intention_2</t>
+  </si>
+  <si>
+    <t>Tricycliques</t>
   </si>
 </sst>
 </file>
@@ -1051,55 +1051,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -1435,7 +1435,7 @@
         <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="K16" t="s">
         <v>77</v>
@@ -1446,19 +1446,19 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
         <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
@@ -1466,90 +1466,90 @@
     </row>
     <row r="18" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>71</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>63</v>
       </c>
       <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" t="s">
         <v>83</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>84</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>85</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>86</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>87</v>
-      </c>
-      <c r="O19" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>63</v>
       </c>
       <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
         <v>91</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>92</v>
-      </c>
-      <c r="E20" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>63</v>
       </c>
       <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" t="s">
-        <v>92</v>
-      </c>
       <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" t="s">
         <v>95</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>96</v>
-      </c>
-      <c r="G21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -1558,62 +1558,62 @@
         <v>77</v>
       </c>
       <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
         <v>99</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>100</v>
       </c>
-      <c r="F22" t="s">
+      <c r="K22" t="s">
         <v>101</v>
-      </c>
-      <c r="K22" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
         <v>63</v>
       </c>
       <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
         <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" t="s">
         <v>63</v>
       </c>
       <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
         <v>84</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F24" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="K24" t="s">
         <v>64</v>
@@ -1621,45 +1621,45 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
       </c>
       <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>114</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" t="s">
         <v>115</v>
       </c>
-      <c r="F25" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" t="s">
         <v>116</v>
-      </c>
-      <c r="H25" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
         <v>120</v>
       </c>
-      <c r="B26" t="s">
-        <v>121</v>
-      </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K26" t="s">
         <v>45</v>
@@ -1667,382 +1667,382 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
         <v>122</v>
       </c>
-      <c r="B27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>123</v>
-      </c>
-      <c r="D27" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
         <v>125</v>
-      </c>
-      <c r="B28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" t="s">
         <v>127</v>
-      </c>
-      <c r="B29" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" t="s">
         <v>129</v>
       </c>
-      <c r="B30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>130</v>
       </c>
-      <c r="D30" t="s">
-        <v>131</v>
-      </c>
       <c r="K30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" t="s">
         <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
         <v>133</v>
       </c>
-      <c r="B32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" t="s">
-        <v>134</v>
-      </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
         <v>135</v>
-      </c>
-      <c r="B33" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
         <v>137</v>
       </c>
-      <c r="B34" t="s">
-        <v>138</v>
-      </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
         <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
         <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" t="s">
         <v>141</v>
-      </c>
-      <c r="K35" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
         <v>144</v>
       </c>
-      <c r="B36" t="s">
-        <v>143</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>141</v>
+      </c>
+      <c r="K36" t="s">
         <v>145</v>
       </c>
-      <c r="E36" t="s">
-        <v>142</v>
-      </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>146</v>
-      </c>
-      <c r="L36" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B39" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" t="s">
         <v>155</v>
       </c>
-      <c r="B40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>156</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>157</v>
-      </c>
-      <c r="E40" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" t="s">
         <v>159</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>160</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>161</v>
       </c>
-      <c r="D41" t="s">
+      <c r="K41" t="s">
         <v>162</v>
-      </c>
-      <c r="K41" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
         <v>164</v>
       </c>
-      <c r="B42" t="s">
-        <v>160</v>
-      </c>
-      <c r="C42" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>165</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>166</v>
-      </c>
-      <c r="F42" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" t="s">
         <v>168</v>
-      </c>
-      <c r="B43" t="s">
-        <v>160</v>
-      </c>
-      <c r="C43" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
         <v>69</v>
       </c>
       <c r="D44" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" t="s">
         <v>171</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>172</v>
-      </c>
-      <c r="F44" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B45" t="s">
-        <v>160</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>175</v>
+      </c>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
         <v>176</v>
-      </c>
-      <c r="B46" t="s">
-        <v>160</v>
-      </c>
-      <c r="C46" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" t="s">
         <v>178</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" t="s">
         <v>179</v>
-      </c>
-      <c r="C47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>180</v>
+      </c>
+      <c r="B48" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" t="s">
         <v>181</v>
-      </c>
-      <c r="B48" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" t="s">
         <v>183</v>
-      </c>
-      <c r="B49" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
       </c>
       <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" t="s">
         <v>186</v>
-      </c>
-      <c r="E50" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="K51" t="s">
         <v>189</v>
-      </c>
-      <c r="K51" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
